--- a/Result/profitability/5356.xlsx
+++ b/Result/profitability/5356.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.155</v>
+        <v>0.235</v>
       </c>
       <c r="N2" t="n">
-        <v>13.3975</v>
+        <v>13.32</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.15625</v>
+        <v>0.20375</v>
       </c>
       <c r="N3" t="n">
-        <v>13.215</v>
+        <v>13.25875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13625</v>
+        <v>0.195</v>
       </c>
       <c r="N4" t="n">
-        <v>13.245</v>
+        <v>13.22125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.12375</v>
+        <v>0.34375</v>
       </c>
       <c r="N5" t="n">
-        <v>13.925</v>
+        <v>13.7225</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26125</v>
+        <v>0.24</v>
       </c>
       <c r="N6" t="n">
-        <v>14.665</v>
+        <v>13.86375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1725</v>
+        <v>0.22875</v>
       </c>
       <c r="N7" t="n">
-        <v>14.85</v>
+        <v>15.0775</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16</v>
+        <v>0.2175</v>
       </c>
       <c r="N8" t="n">
-        <v>16.37625</v>
+        <v>16.5925</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.02</v>
       </c>
       <c r="M10" t="n">
-        <v>0.50625</v>
+        <v>0.5062500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>18.0825</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>992</v>
+      </c>
+      <c r="D75" t="n">
+        <v>865</v>
+      </c>
+      <c r="E75" t="n">
+        <v>127</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>25</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>76</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.4575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.642857142857143</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1557155715571557</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.725490196078431</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.620000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1120331950207469</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
